--- a/api/templates/device_and_site_summary_report/uk.xlsx
+++ b/api/templates/device_and_site_summary_report/uk.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\xpert_site_summary_report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_and_site_summary_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A849D3-EAC1-4FD4-9C61-2E8912199BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6C80A9-15EA-444D-BB00-D3743347A208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="760" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Зведений звіт Xpert по сайту" sheetId="1" r:id="rId1"/>
-    <sheet name="Xpert Інвентаризація сайту" sheetId="2" r:id="rId2"/>
-    <sheet name="Помилки сайту Xpert за пристроя" sheetId="3" r:id="rId3"/>
+    <sheet name="Короткий опис пристрою та сайту" sheetId="1" r:id="rId1"/>
+    <sheet name="Інвентаризація" sheetId="2" r:id="rId2"/>
+    <sheet name="Помилки за пристроями" sheetId="3" r:id="rId3"/>
     <sheet name="Коди помилок" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -371,17 +371,17 @@
     <t>Виявлена втрата сигналу на кривій підсилення</t>
   </si>
   <si>
-    <t>Пристрої Xpert</t>
-  </si>
-  <si>
-    <t>Інвентаризація Xpert за сайтом</t>
-  </si>
-  <si>
-    <t>Помилки Xpert за пристроями</t>
-  </si>
-  <si>
     <t>Оновлення останнього
 результату</t>
+  </si>
+  <si>
+    <t>Зведений звіт про пристрій та сайт</t>
+  </si>
+  <si>
+    <t>Інвентаризація пристроїв та об'єктів</t>
+  </si>
+  <si>
+    <t>Помилки за пристроями</t>
   </si>
 </sst>
 </file>
@@ -556,6 +556,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -566,9 +569,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -953,85 +953,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T11"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="15.125" customWidth="1"/>
-    <col min="5" max="5" width="31.375" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14.625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.375" style="4" customWidth="1"/>
-    <col min="12" max="14" width="14.375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" style="4" customWidth="1"/>
+    <col min="12" max="14" width="14.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="3" customWidth="1"/>
     <col min="16" max="16" width="10.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="18.125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" style="3" customWidth="1"/>
     <col min="18" max="18" width="11" style="4" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="1015" max="1024" width="9.125" customWidth="1"/>
+    <col min="1015" max="1024" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="1:20" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>7</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>12</v>
@@ -1093,7 +1093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>26</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="16"/>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -1179,68 +1179,68 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="45" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>47</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>55</v>
       </c>
@@ -1304,46 +1304,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.125" customWidth="1"/>
-    <col min="2" max="9" width="8.625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" customWidth="1"/>
+    <col min="2" max="9" width="8.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" style="3" customWidth="1"/>
     <col min="12" max="12" width="15.5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
         <v>6</v>
       </c>
@@ -1351,30 +1351,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="26" t="s">
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="L8" s="26" t="s">
+      <c r="L8" s="27" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
+    <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="25"/>
       <c r="B9" s="1">
         <v>5011</v>
       </c>
@@ -1402,10 +1402,10 @@
       <c r="J9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>67</v>
       </c>
@@ -1459,14 +1459,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="39.125" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
+    <col min="1" max="1" width="5.1640625" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" customWidth="1"/>
+    <col min="3" max="3" width="100.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>78</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19">
         <v>1001</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19">
         <v>1002</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19">
         <v>1004</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="19">
         <v>1005</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19">
         <v>1006</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
         <v>1007</v>
       </c>
@@ -1543,7 +1543,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
         <v>1017</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
         <v>1018</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
         <v>2003</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19">
         <v>2005</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
         <v>2008</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
         <v>2009</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
         <v>2011</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
         <v>2014</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
         <v>2016</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
         <v>2018</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
         <v>2022</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="19">
         <v>2025</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
         <v>2032</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
         <v>2034</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
         <v>2037</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19">
         <v>4010</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="19">
         <v>4017</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>5006</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19">
         <v>5007</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
         <v>5011</v>
       </c>

--- a/api/templates/device_and_site_summary_report/uk.xlsx
+++ b/api/templates/device_and_site_summary_report/uk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_and_site_summary_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6C80A9-15EA-444D-BB00-D3743347A208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1F104D-A30B-004B-A7DD-C2CAB2B9C421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="760" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="760" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Короткий опис пристрою та сайту" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,6 @@
     <t>Дати: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>Примітки. Категорії результатів представлені всіма можливими комбінаціями результатів, які GeneXpert надсилає до Aspect. Наприклад, MTB Detected не включає MTB Detected Rif Detected, оскільки вони вважаються різними результатами</t>
-  </si>
-  <si>
     <t>Області: &lt;States&gt;</t>
   </si>
   <si>
@@ -382,6 +379,9 @@
   </si>
   <si>
     <t>Помилки за пристроями</t>
+  </si>
+  <si>
+    <t>Примітки. Категорії результатів представляють усі можливі комбінації результатів, які пристрій надсилає до Aspect. Наприклад, MTB Detected не включає MTB Detected і Rif Detected, оскільки вони вважаються різними результатами</t>
   </si>
 </sst>
 </file>
@@ -973,7 +973,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -985,14 +985,14 @@
         <v>0</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" s="23"/>
       <c r="F4" s="23"/>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5" spans="1:20" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="23"/>
       <c r="F5" s="23"/>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="23"/>
       <c r="F6" s="23"/>
@@ -1026,133 +1026,133 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="L8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="S8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="T8" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="G9" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="I9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="J9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="K9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="L9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="N9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="O9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="P9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="Q9" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="R9" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="R9" s="15" t="s">
+      <c r="S9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="T9" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="T9" s="11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
@@ -1193,7 +1193,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
@@ -1213,83 +1213,83 @@
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="H9" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1315,7 +1315,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1325,27 +1325,27 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -1353,10 +1353,10 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
@@ -1367,10 +1367,10 @@
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
       <c r="K8" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="27" t="s">
         <v>64</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1400,44 +1400,44 @@
         <v>2022</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K9" s="27"/>
       <c r="L9" s="27"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="L10" s="3" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
@@ -1468,13 +1468,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1482,10 +1482,10 @@
         <v>1001</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>81</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1493,10 +1493,10 @@
         <v>1002</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1504,10 +1504,10 @@
         <v>1004</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1515,10 +1515,10 @@
         <v>1005</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1526,10 +1526,10 @@
         <v>1006</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1537,10 +1537,10 @@
         <v>1007</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1548,10 +1548,10 @@
         <v>1017</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1559,10 +1559,10 @@
         <v>1018</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1570,10 +1570,10 @@
         <v>2003</v>
       </c>
       <c r="B10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1581,10 +1581,10 @@
         <v>2005</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1592,10 +1592,10 @@
         <v>2008</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1603,10 +1603,10 @@
         <v>2009</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1614,10 +1614,10 @@
         <v>2011</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1625,10 +1625,10 @@
         <v>2014</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1636,10 +1636,10 @@
         <v>2016</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1647,10 +1647,10 @@
         <v>2018</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1658,10 +1658,10 @@
         <v>2022</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1669,10 +1669,10 @@
         <v>2025</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1680,10 +1680,10 @@
         <v>2032</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1691,10 +1691,10 @@
         <v>2034</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1702,10 +1702,10 @@
         <v>2037</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1713,10 +1713,10 @@
         <v>4010</v>
       </c>
       <c r="B23" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>104</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1724,10 +1724,10 @@
         <v>4017</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1735,10 +1735,10 @@
         <v>5006</v>
       </c>
       <c r="B25" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>106</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1746,10 +1746,10 @@
         <v>5007</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1757,10 +1757,10 @@
         <v>5011</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/device_and_site_summary_report/uk.xlsx
+++ b/api/templates/device_and_site_summary_report/uk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_and_site_summary_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1F104D-A30B-004B-A7DD-C2CAB2B9C421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01197FBB-B3C8-0348-B62C-2DA6B57BFEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4360" yWindow="760" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="115">
   <si>
     <t>Дати: &lt;Dates&gt;</t>
   </si>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t>Примітки. Категорії результатів представляють усі можливі комбінації результатів, які пристрій надсилає до Aspect. Наприклад, MTB Detected не включає MTB Detected і Rif Detected, оскільки вони вважаються різними результатами</t>
+  </si>
+  <si>
+    <t>#SUM_DYNAMIC</t>
   </si>
 </sst>
 </file>
@@ -392,7 +395,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -431,8 +434,28 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -445,8 +468,20 @@
         <bgColor rgb="FF00CCFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CC0DD"/>
+        <bgColor rgb="FF3CC0DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABEBEF"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -495,19 +530,128 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -545,9 +689,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -569,6 +710,50 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -656,9 +841,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -696,7 +881,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -802,7 +987,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -944,7 +1129,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -952,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="27" customWidth="1"/>
@@ -960,207 +1145,238 @@
     <col min="5" max="5" width="31.33203125" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" style="4" customWidth="1"/>
-    <col min="12" max="14" width="14.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.1640625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="10.5" style="3" customWidth="1"/>
-    <col min="17" max="17" width="18.1640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="11" style="4" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" style="3" customWidth="1"/>
+    <col min="12" max="14" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="10.5" style="2" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11" style="3" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="1015" max="1024" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:21" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-    </row>
-    <row r="5" spans="1:20" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:21" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:20" s="10" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:21" s="9" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="N8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="Q8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="R8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="S8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="T8" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="O9" s="14" t="s">
+      <c r="O9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="P9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="Q9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="R9" s="15" t="s">
+      <c r="R9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="S9" s="11" t="s">
+      <c r="S9" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T9" s="11" t="s">
+      <c r="T9" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+    <row r="10" spans="1:21" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39">
+        <f>SUM(S$9:S9)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="39">
+        <f>SUM(T$9:T9)</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1192,24 +1408,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1222,7 +1438,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="34" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1230,65 +1446,65 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1307,14 +1523,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
-    <col min="2" max="9" width="8.6640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="12.1640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.5" style="3" customWidth="1"/>
+    <col min="2" max="9" width="8.6640625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.1640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1334,7 +1550,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1344,37 +1560,37 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="27" t="s">
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="27" t="s">
+      <c r="L8" s="25" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="25"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="1">
         <v>5011</v>
       </c>
@@ -1402,44 +1618,44 @@
       <c r="J9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="L10" s="3" t="e">
+      <c r="L10" s="13" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
@@ -1458,311 +1674,1287 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:D1001"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.1640625" customWidth="1"/>
-    <col min="2" max="2" width="39.1640625" customWidth="1"/>
-    <col min="3" max="3" width="100.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="39.1640625" customWidth="1"/>
+    <col min="4" max="4" width="74.1640625" customWidth="1"/>
+    <col min="5" max="7" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C2" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D2" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
+    <row r="3" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="27">
         <v>1001</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C3" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D3" s="29" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19">
+    <row r="4" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="30">
         <v>1002</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C4" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D4" s="32" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19">
+    <row r="5" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="33">
         <v>1004</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C5" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D5" s="35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19">
+    <row r="6" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="30">
         <v>1005</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C6" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D6" s="32" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+    <row r="7" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="33">
         <v>1006</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="C7" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D7" s="35" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="19">
+    <row r="8" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="30">
         <v>1007</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="C8" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D8" s="32" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="19">
+    <row r="9" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="33">
         <v>1017</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="C9" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="D9" s="35" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19">
+    <row r="10" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="30">
         <v>1018</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="C10" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D10" s="32" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19">
+    <row r="11" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="33">
         <v>2003</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="C11" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="D11" s="35" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19">
+    <row r="12" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="30">
         <v>2005</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="C12" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="D12" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
+    <row r="13" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="33">
         <v>2008</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C13" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="D13" s="35" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19">
+    <row r="14" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="30">
         <v>2009</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="C14" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="D14" s="32" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
+    <row r="15" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="33">
         <v>2011</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="C15" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D15" s="35" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19">
+    <row r="16" spans="2:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="B16" s="30">
         <v>2014</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="C16" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D16" s="32" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19">
+    <row r="17" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="33">
         <v>2016</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="C17" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="D17" s="35" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="19">
+    <row r="18" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="30">
         <v>2018</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="C18" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="D18" s="32" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="19">
+    <row r="19" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="33">
         <v>2022</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="C19" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="D19" s="35" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19">
+    <row r="20" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="30">
         <v>2025</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="C20" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="D20" s="32" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="19">
+    <row r="21" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="33">
         <v>2032</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="C21" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="D21" s="35" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="19">
+    <row r="22" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="30">
         <v>2034</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="C22" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="D22" s="32" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="19">
+    <row r="23" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="33">
         <v>2037</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="C23" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="D23" s="35" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19">
+    <row r="24" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="30">
         <v>4010</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="C24" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="D24" s="32" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19">
+    <row r="25" spans="2:4" ht="51" x14ac:dyDescent="0.2">
+      <c r="B25" s="33">
         <v>4017</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="C25" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="D25" s="35" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="19">
+    <row r="26" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="30">
         <v>5006</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="C26" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="D26" s="32" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19">
+    <row r="27" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="33">
         <v>5007</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="C27" s="34" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="D27" s="35" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="19">
+    <row r="28" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="36">
         <v>5011</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="C28" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="D28" s="38" t="s">
         <v>108</v>
       </c>
     </row>
+    <row r="29" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/api/templates/device_and_site_summary_report/uk.xlsx
+++ b/api/templates/device_and_site_summary_report/uk.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="152">
   <si>
     <t>Зведений звіт про пристрій та сайт</t>
   </si>
@@ -26,9 +26,6 @@
     <t>Дати: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>Примітки. Категорії результатів представляють усі можливі комбінації результатів, які пристрій надсилає до Aspect. Наприклад, MTB Detected не включає MTB Detected і Rif Detected, оскільки вони вважаються різними результатами</t>
-  </si>
-  <si>
     <t>Області: &lt;States&gt;</t>
   </si>
   <si>
@@ -57,9 +54,6 @@
   </si>
   <si>
     <t>Серійний</t>
-  </si>
-  <si>
-    <t>Серійний номер приладу</t>
   </si>
   <si>
     <t xml:space="preserve">Оновлення останнього
@@ -121,9 +115,6 @@
   </si>
   <si>
     <t>&lt;serial&gt;</t>
-  </si>
-  <si>
-    <t>&lt;instrumentSerial&gt;</t>
   </si>
   <si>
     <t>&lt;lastUploadOn&gt;</t>
@@ -1436,17 +1427,16 @@
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="4" width="27" customWidth="1"/>
     <col min="5" max="5" width="15.1640625" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" style="1" customWidth="1"/>
-    <col min="12" max="15" width="14.33203125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.1640625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="18.1640625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11" style="2" customWidth="1"/>
-    <col min="20" max="20" width="14" customWidth="1"/>
-    <col min="1016" max="1025" width="9.1640625" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" style="1" customWidth="1"/>
+    <col min="11" max="14" width="14.33203125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5" style="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11" style="2" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="1015" max="1024" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1456,192 +1446,183 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="F2" s="4"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="H2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="H3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="H4"/>
     </row>
     <row r="5" ht="17" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="H5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="H6"/>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
     </row>
     <row r="8" ht="67.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="K8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="L8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="S8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="I9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="J9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="K9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="L9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="M9" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="N9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="O9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="P9" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="Q9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="R9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="S9" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="T9" s="14" t="s">
         <v>46</v>
-      </c>
-      <c r="S9" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="T9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="U9" s="14" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -1660,15 +1641,14 @@
       <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16">
+      <c r="S10" s="16">
         <f>SUM(T$9:T9)</f>
       </c>
-      <c r="U10" s="17">
+      <c r="T10" s="17">
         <f>SUM(U$9:U9)</f>
       </c>
-      <c r="V10" s="18" t="s">
-        <v>51</v>
+      <c r="U10" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
@@ -1676,7 +1656,6 @@
       <c r="C11" s="19"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1710,7 +1689,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -1721,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
@@ -1730,92 +1709,92 @@
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="26"/>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="25"/>
       <c r="D7" s="26"/>
     </row>
     <row r="8" ht="54" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="G9" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="H9" s="27" t="s">
         <v>65</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>68</v>
       </c>
       <c r="I9" s="27"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B10" s="30"/>
       <c r="C10" s="31" t="e">
@@ -1870,7 +1849,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1880,27 +1859,27 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -1908,10 +1887,10 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C8" s="38"/>
       <c r="D8" s="38"/>
@@ -1922,10 +1901,10 @@
       <c r="I8" s="38"/>
       <c r="J8" s="39"/>
       <c r="K8" s="54" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L8" s="54" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1955,44 +1934,44 @@
         <v>2022</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K9" s="40"/>
       <c r="L9" s="40"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B10" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="F10" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="G10" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="H10" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="I10" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="J10" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="H10" s="43" t="s">
+      <c r="K10" s="43" t="s">
         <v>114</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="J10" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="K10" s="43" t="s">
-        <v>117</v>
       </c>
       <c r="L10" s="43" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
@@ -2001,7 +1980,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="48">
         <f>SUM(B$10:B10)</f>
@@ -2080,13 +2059,13 @@
     <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="56" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2094,10 +2073,10 @@
         <v>1001</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2105,10 +2084,10 @@
         <v>1002</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2116,10 +2095,10 @@
         <v>1004</v>
       </c>
       <c r="C5" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="65" t="s">
         <v>126</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2127,10 +2106,10 @@
         <v>1005</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2138,10 +2117,10 @@
         <v>1006</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2149,10 +2128,10 @@
         <v>1007</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2160,10 +2139,10 @@
         <v>1017</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2171,10 +2150,10 @@
         <v>1018</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2182,10 +2161,10 @@
         <v>2003</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2193,10 +2172,10 @@
         <v>2005</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D12" s="62" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2204,10 +2183,10 @@
         <v>2008</v>
       </c>
       <c r="C13" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="65" t="s">
         <v>135</v>
-      </c>
-      <c r="D13" s="65" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="14" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2215,10 +2194,10 @@
         <v>2009</v>
       </c>
       <c r="C14" s="61" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="62" t="s">
         <v>135</v>
-      </c>
-      <c r="D14" s="62" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2226,10 +2205,10 @@
         <v>2011</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" ht="51" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2237,10 +2216,10 @@
         <v>2014</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2248,10 +2227,10 @@
         <v>2016</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D17" s="65" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2259,10 +2238,10 @@
         <v>2018</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D18" s="62" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2270,10 +2249,10 @@
         <v>2022</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D19" s="65" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2281,10 +2260,10 @@
         <v>2025</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2292,10 +2271,10 @@
         <v>2032</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2303,10 +2282,10 @@
         <v>2034</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D22" s="62" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2314,10 +2293,10 @@
         <v>2037</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2325,10 +2304,10 @@
         <v>4010</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" ht="51" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2336,10 +2315,10 @@
         <v>4017</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D25" s="65" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2347,10 +2326,10 @@
         <v>5006</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2358,10 +2337,10 @@
         <v>5007</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D27" s="65" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2369,10 +2348,10 @@
         <v>5011</v>
       </c>
       <c r="C28" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" s="68" t="s">
         <v>151</v>
-      </c>
-      <c r="D28" s="68" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3385,7 +3364,7 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -3457,7 +3436,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -3493,7 +3472,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B4" s="33"/>
       <c r="C4" s="33"/>
@@ -3597,7 +3576,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="33">
         <v>2</v>
@@ -3635,67 +3614,67 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="E8" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="F8" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="G8" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="H8" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="I8" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="J8" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="K8" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="36" t="s">
+      <c r="L8" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="M8" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="K8" s="36" t="s">
+      <c r="N8" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="O8" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="M8" s="36" t="s">
+      <c r="P8" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="N8" s="36" t="s">
+      <c r="Q8" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="O8" s="36" t="s">
+      <c r="R8" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="P8" s="36" t="s">
+      <c r="S8" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="Q8" s="36" t="s">
+      <c r="T8" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="R8" s="36" t="s">
+      <c r="U8" s="37" t="s">
         <v>89</v>
-      </c>
-      <c r="S8" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="T8" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="U8" s="37" t="s">
-        <v>92</v>
       </c>
       <c r="V8" s="38"/>
       <c r="W8" s="38"/>
@@ -3706,13 +3685,13 @@
       <c r="AB8" s="38"/>
       <c r="AC8" s="39"/>
       <c r="AD8" s="35" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="AE8" s="35" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AF8" s="35" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
@@ -3761,7 +3740,7 @@
         <v>2022</v>
       </c>
       <c r="AC9" s="41" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AD9" s="40"/>
       <c r="AE9" s="40"/>
@@ -3769,36 +3748,36 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="E10" s="43" t="s">
         <v>98</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>101</v>
       </c>
       <c r="F10" s="44">
         <f>IFERROR(IF(A10="No data","",IF(C10=0,0,D10/C10)),0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H10" s="45">
         <f>IFERROR(IF(A10="No data","",IF(B10&lt;&gt;0, G10/B10, 0)),0)</f>
         <v>0</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="J10" s="43" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K10" s="43">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10),0)</f>
@@ -3821,53 +3800,53 @@
         <v>0</v>
       </c>
       <c r="P10" s="43" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q10" s="43" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R10" s="43" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S10" s="44">
         <f>IFERROR(IF(A10="No data","",IF(I10=0,0,R10/I10)),0)</f>
         <v>0</v>
       </c>
       <c r="T10" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="U10" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="V10" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="W10" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="U10" s="43" t="s">
+      <c r="X10" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="V10" s="43" t="s">
+      <c r="Y10" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="W10" s="43" t="s">
+      <c r="Z10" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="X10" s="43" t="s">
+      <c r="AA10" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="Y10" s="43" t="s">
+      <c r="AB10" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="Z10" s="43" t="s">
+      <c r="AC10" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="AA10" s="43" t="s">
+      <c r="AD10" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="AB10" s="43" t="s">
+      <c r="AE10" s="43" t="s">
         <v>115</v>
-      </c>
-      <c r="AC10" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="AD10" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE10" s="43" t="s">
-        <v>118</v>
       </c>
       <c r="AF10" s="43">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10+AE10),0)</f>
@@ -3876,7 +3855,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>

--- a/api/templates/device_and_site_summary_report/uk.xlsx
+++ b/api/templates/device_and_site_summary_report/uk.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="153">
   <si>
     <t>Зведений звіт про пристрій та сайт</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>аналіз: &lt;Assays&gt;</t>
+  </si>
+  <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -1420,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11.1640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="34.5" customWidth="1"/>
@@ -1439,7 +1442,7 @@
     <col min="1015" max="1024" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1489,173 +1492,178 @@
       <c r="G6" s="4"/>
       <c r="H6"/>
     </row>
-    <row r="7" ht="17" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" ht="67.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    </row>
+    <row r="8" ht="17" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" ht="67.5" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="K9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="L9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="M9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="N9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="O9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="P9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="Q9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S8" s="8" t="s">
+      <c r="R9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="S9" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="T9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="10" t="s">
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="B10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="C10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="I10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="J10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="K10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="L10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="N9" s="13" t="s">
+      <c r="M10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="N10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="O10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="13" t="s">
+      <c r="P10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="R9" s="12" t="s">
+      <c r="Q10" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="R10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="T9" s="14" t="s">
+      <c r="S10" s="14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="T10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16">
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16">
         <f>SUM(T$9:T9)</f>
       </c>
-      <c r="T10" s="17">
+      <c r="T11" s="17">
         <f>SUM(U$9:U9)</f>
       </c>
-      <c r="U10" s="18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
+      <c r="U11" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1673,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1689,7 +1697,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="21"/>
       <c r="C1" s="21"/>
@@ -1700,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
@@ -1729,101 +1737,101 @@
       <c r="C6" s="25"/>
       <c r="D6" s="26"/>
     </row>
-    <row r="7" ht="17" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-    </row>
-    <row r="8" ht="54" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    </row>
+    <row r="8" ht="17" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
+    </row>
+    <row r="9" ht="54" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="D9" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="E9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="27" t="s">
+      <c r="I9" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="28" t="s">
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="C10" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="D10" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="E10" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="F10" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="G10" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="27"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31" t="e">
+      <c r="H10" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="27"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="31" t="e">
         <f>AVERAGE(C$9:C9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D11" s="30">
         <f>SUM(D$9:D9)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="30">
+      </c>
+      <c r="E11" s="30">
         <f>SUM(E$9:E9)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="30">
+      </c>
+      <c r="F11" s="30">
         <f>SUM(F$9:F9)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="31" t="e">
+      </c>
+      <c r="G11" s="31" t="e">
         <f>AVERAGE(G$9:G9)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="30">
+      <c r="H11" s="30">
         <f>SUM(H$9:H9)</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="32">
+      </c>
+      <c r="I11" s="32">
         <f>SUM(I$9:I9)</f>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1837,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.6640625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
@@ -1849,7 +1857,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1877,162 +1885,157 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="52" t="s">
+    <row r="7" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+    </row>
+    <row r="8" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="L8" s="54" t="s">
+    <row r="9" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="54" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="9" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="40"/>
-      <c r="B9" s="41">
+      <c r="L9" s="54" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" ht="31.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="40"/>
+      <c r="B10" s="41">
         <v>5011</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C10" s="41">
         <v>5007</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D10" s="41">
         <v>5006</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E10" s="41">
         <v>2008</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F10" s="41">
         <v>2005</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G10" s="41">
         <v>2037</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H10" s="41">
         <v>2025</v>
       </c>
-      <c r="I9" s="41">
+      <c r="I10" s="41">
         <v>2022</v>
       </c>
-      <c r="J9" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="43" t="s">
+      <c r="J10" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="C11" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="D11" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="E11" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="F11" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="H10" s="43" t="s">
+      <c r="G11" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="I10" s="43" t="s">
+      <c r="H11" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="J10" s="43" t="s">
+      <c r="I11" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="K10" s="43" t="s">
+      <c r="J11" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="L10" s="43" t="e">
+      <c r="K11" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="L11" s="43" t="e">
         <f>B10+C10+D10+E10+F10+G10+H10+I10+J10+K10</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="48">
+    <row r="12" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="48">
         <f>SUM(B$10:B10)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="48">
+      </c>
+      <c r="C12" s="48">
         <f>SUM(C$10:C10)</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="48">
+      </c>
+      <c r="D12" s="48">
         <f>SUM(D$10:D10)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="48">
+      </c>
+      <c r="E12" s="48">
         <f>SUM(E$10:E10)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="48">
+      </c>
+      <c r="F12" s="48">
         <f>SUM(F$10:F10)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="48">
+      </c>
+      <c r="G12" s="48">
         <f>SUM(G$10:G10)</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="48">
+      </c>
+      <c r="H12" s="48">
         <f>SUM(H$10:H10)</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="48">
+      </c>
+      <c r="I12" s="48">
         <f>SUM(I$10:I10)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="48">
+      </c>
+      <c r="J12" s="48">
         <f>SUM(J$10:J10)</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="48">
+      </c>
+      <c r="K12" s="48">
         <f>SUM(K$10:K10)</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="55" t="e">
+      </c>
+      <c r="L12" s="55" t="e">
         <f>SUM(L$10:L10)</f>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <conditionalFormatting sqref="L10">
     <cfRule type="notContainsBlanks" dxfId="2" priority="1" operator="notContainsBlanks">
@@ -2059,13 +2062,13 @@
     <row r="1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2073,10 +2076,10 @@
         <v>1001</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2084,10 +2087,10 @@
         <v>1002</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2095,10 +2098,10 @@
         <v>1004</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D5" s="65" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2106,10 +2109,10 @@
         <v>1005</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2117,10 +2120,10 @@
         <v>1006</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D7" s="65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2128,10 +2131,10 @@
         <v>1007</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2139,10 +2142,10 @@
         <v>1017</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2150,10 +2153,10 @@
         <v>1018</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2161,10 +2164,10 @@
         <v>2003</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2172,10 +2175,10 @@
         <v>2005</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D12" s="62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2183,10 +2186,10 @@
         <v>2008</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D13" s="65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2194,10 +2197,10 @@
         <v>2009</v>
       </c>
       <c r="C14" s="61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D14" s="62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2205,10 +2208,10 @@
         <v>2011</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" ht="51" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2216,10 +2219,10 @@
         <v>2014</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D16" s="62" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2227,10 +2230,10 @@
         <v>2016</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D17" s="65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2238,10 +2241,10 @@
         <v>2018</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D18" s="62" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2249,10 +2252,10 @@
         <v>2022</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" s="65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2260,10 +2263,10 @@
         <v>2025</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2271,10 +2274,10 @@
         <v>2032</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2282,10 +2285,10 @@
         <v>2034</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D22" s="62" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2293,10 +2296,10 @@
         <v>2037</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2304,10 +2307,10 @@
         <v>4010</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" ht="51" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2315,10 +2318,10 @@
         <v>4017</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D25" s="65" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2326,10 +2329,10 @@
         <v>5006</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2337,10 +2340,10 @@
         <v>5007</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D27" s="65" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" ht="21.75" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
@@ -2348,10 +2351,10 @@
         <v>5011</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D28" s="68" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3364,7 +3367,7 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -3436,7 +3439,7 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -3472,7 +3475,7 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="33"/>
       <c r="C4" s="33"/>
@@ -3507,7 +3510,9 @@
       <c r="AF4" s="33"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
+      <c r="A5" s="23" t="s">
+        <v>6</v>
+      </c>
       <c r="B5" s="33"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
@@ -3576,7 +3581,7 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="33">
         <v>2</v>
@@ -3614,67 +3619,67 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" s="36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L8" s="36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M8" s="36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N8" s="36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O8" s="36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P8" s="36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R8" s="36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="S8" s="36" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="T8" s="36" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U8" s="37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V8" s="38"/>
       <c r="W8" s="38"/>
@@ -3685,13 +3690,13 @@
       <c r="AB8" s="38"/>
       <c r="AC8" s="39"/>
       <c r="AD8" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE8" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF8" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
@@ -3740,7 +3745,7 @@
         <v>2022</v>
       </c>
       <c r="AC9" s="41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AD9" s="40"/>
       <c r="AE9" s="40"/>
@@ -3748,36 +3753,36 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F10" s="44">
         <f>IFERROR(IF(A10="No data","",IF(C10=0,0,D10/C10)),0)</f>
         <v>0</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" s="45">
         <f>IFERROR(IF(A10="No data","",IF(B10&lt;&gt;0, G10/B10, 0)),0)</f>
         <v>0</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J10" s="43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K10" s="43">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10),0)</f>
@@ -3800,53 +3805,53 @@
         <v>0</v>
       </c>
       <c r="P10" s="43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q10" s="43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R10" s="43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S10" s="44">
         <f>IFERROR(IF(A10="No data","",IF(I10=0,0,R10/I10)),0)</f>
         <v>0</v>
       </c>
       <c r="T10" s="46" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="U10" s="43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="V10" s="43" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="W10" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X10" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y10" s="43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z10" s="43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA10" s="43" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AB10" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AC10" s="43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AD10" s="43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AE10" s="43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AF10" s="43">
         <f>IFERROR(IF(A10="No data","",U10+V10+W10+X10+Y10+Z10+AA10+AB10+AC10+AD10+AE10),0)</f>
@@ -3855,7 +3860,7 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
